--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T16:58:25+00:00</t>
+    <t>2025-02-25T17:04:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T17:04:42+00:00</t>
+    <t>2025-02-26T16:08:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T16:08:18+00:00</t>
+    <t>2025-02-27T08:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T08:43:40+00:00</t>
+    <t>2025-02-27T14:19:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:19:46+00:00</t>
+    <t>2025-03-07T08:37:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T08:37:17+00:00</t>
+    <t>2025-03-11T13:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:02:31+00:00</t>
+    <t>2025-03-14T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T12:41:19+00:00</t>
+    <t>2025-03-25T09:33:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T09:33:15+00:00</t>
+    <t>2025-05-19T13:21:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T13:21:22+00:00</t>
+    <t>2025-06-03T15:31:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-03T15:31:08+00:00</t>
+    <t>2025-06-03T16:16:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-03T16:16:13+00:00</t>
+    <t>2025-06-04T08:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T08:06:36+00:00</t>
+    <t>2025-06-04T14:37:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T14:37:49+00:00</t>
+    <t>2025-06-04T15:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T15:14:11+00:00</t>
+    <t>2025-06-11T10:56:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T10:56:37+00:00</t>
+    <t>2025-06-11T12:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T12:34:17+00:00</t>
+    <t>2025-06-11T14:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T14:35:18+00:00</t>
+    <t>2025-06-12T14:08:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12T14:08:06+00:00</t>
+    <t>2025-06-16T10:40:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T10:40:18+00:00</t>
+    <t>2025-06-16T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T15:31:48+00:00</t>
+    <t>2025-06-17T11:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-17T11:26:30+00:00</t>
+    <t>2025-06-18T08:23:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-18T08:23:39+00:00</t>
+    <t>2025-06-18T10:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-18T10:20:00+00:00</t>
+    <t>2025-06-19T11:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-19T11:33:33+00:00</t>
+    <t>2025-06-19T12:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-19T12:18:09+00:00</t>
+    <t>2025-06-19T14:16:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-19T14:16:36+00:00</t>
+    <t>2025-06-23T13:32:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T13:32:18+00:00</t>
+    <t>2025-06-30T12:13:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-30T12:13:52+00:00</t>
+    <t>2025-07-02T12:17:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-02T12:17:31+00:00</t>
+    <t>2025-07-02T14:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-02T14:11:11+00:00</t>
+    <t>2025-07-08T14:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T14:18:27+00:00</t>
+    <t>2025-07-11T07:31:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-11T07:31:28+00:00</t>
+    <t>2025-07-11T10:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-11T10:08:59+00:00</t>
+    <t>2025-07-16T12:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T12:42:07+00:00</t>
+    <t>2025-07-16T15:09:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T15:09:46+00:00</t>
+    <t>2025-07-17T14:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-17T14:23:37+00:00</t>
+    <t>2025-07-18T07:52:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-18T07:52:12+00:00</t>
+    <t>2025-07-28T09:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-28T09:55:12+00:00</t>
+    <t>2025-07-28T16:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-28T16:12:17+00:00</t>
+    <t>2025-07-30T09:57:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T09:57:17+00:00</t>
+    <t>2025-09-04T08:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-04T08:14:57+00:00</t>
+    <t>2025-09-18T06:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T06:32:12+00:00</t>
+    <t>2025-09-18T11:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T11:04:21+00:00</t>
+    <t>2025-09-18T14:06:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T14:06:27+00:00</t>
+    <t>2025-09-18T16:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T16:36:10+00:00</t>
+    <t>2025-10-13T09:02:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T09:02:22+00:00</t>
+    <t>2025-10-13T11:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T11:17:15+00:00</t>
+    <t>2025-10-13T12:32:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T12:32:46+00:00</t>
+    <t>2025-10-13T13:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T13:38:16+00:00</t>
+    <t>2025-10-13T14:51:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T14:51:45+00:00</t>
+    <t>2025-10-14T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T07:40:12+00:00</t>
+    <t>2025-10-14T09:41:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T09:41:04+00:00</t>
+    <t>2025-10-14T11:48:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T11:48:11+00:00</t>
+    <t>2025-10-14T13:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T13:06:01+00:00</t>
+    <t>2025-10-14T14:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T14:12:23+00:00</t>
+    <t>2025-10-14T15:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T15:10:58+00:00</t>
+    <t>2025-10-14T17:45:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T17:45:09+00:00</t>
+    <t>2025-10-15T07:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-15T07:59:39+00:00</t>
+    <t>2025-10-15T12:33:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-15T12:33:07+00:00</t>
+    <t>2025-10-15T13:56:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-15T13:56:08+00:00</t>
+    <t>2025-10-29T16:41:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T16:41:38+00:00</t>
+    <t>2025-10-31T08:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T08:16:32+00:00</t>
+    <t>2025-11-03T20:06:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-03T20:06:17+00:00</t>
+    <t>2025-11-04T18:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-04T18:14:37+00:00</t>
+    <t>2025-11-04T21:20:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-04T21:20:50+00:00</t>
+    <t>2025-11-05T09:19:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T09:19:17+00:00</t>
+    <t>2025-11-05T12:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T12:12:06+00:00</t>
+    <t>2025-11-05T14:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T14:25:10+00:00</t>
+    <t>2025-11-07T09:51:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T09:51:42+00:00</t>
+    <t>2025-11-07T14:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T14:39:45+00:00</t>
+    <t>2025-11-07T16:06:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T16:06:45+00:00</t>
+    <t>2025-11-12T17:02:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-12T17:02:37+00:00</t>
+    <t>2025-11-12T18:15:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-12T18:15:08+00:00</t>
+    <t>2025-11-20T16:01:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T16:01:06+00:00</t>
+    <t>2025-11-26T08:37:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-26T08:37:36+00:00</t>
+    <t>2025-11-27T08:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T08:43:00+00:00</t>
+    <t>2025-11-28T09:15:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T09:15:19+00:00</t>
+    <t>2025-11-28T13:41:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T13:41:04+00:00</t>
+    <t>2025-12-08T15:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-08T15:29:34+00:00</t>
+    <t>2025-12-08T17:18:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-08T17:18:19+00:00</t>
+    <t>2025-12-10T13:53:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-10T13:53:18+00:00</t>
+    <t>2025-12-11T13:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T13:50:41+00:00</t>
+    <t>2025-12-15T15:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T15:13:27+00:00</t>
+    <t>2025-12-20T13:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-20T13:25:39+00:00</t>
+    <t>2026-01-07T09:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T09:16:12+00:00</t>
+    <t>2026-01-08T09:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T09:55:22+00:00</t>
+    <t>2026-01-15T10:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T10:06:16+00:00</t>
+    <t>2026-03-09T11:39:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:39:04+00:00</t>
+    <t>2026-03-10T13:56:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T13:56:55+00:00</t>
+    <t>2026-03-13T11:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T11:12:59+00:00</t>
+    <t>2026-03-13T14:08:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:08:07+00:00</t>
+    <t>2026-03-16T09:36:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T09:36:58+00:00</t>
+    <t>2026-04-15T12:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:25:44+00:00</t>
+    <t>2026-04-21T11:09:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:09:45+00:00</t>
+    <t>2026-04-21T12:38:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T12:38:05+00:00</t>
+    <t>2026-04-21T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:44:55+00:00</t>
+    <t>2026-04-21T15:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T15:54:01+00:00</t>
+    <t>2026-04-22T10:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:26+00:00</t>
+    <t>2026-04-23T19:56:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T19:56:15+00:00</t>
+    <t>2026-04-24T09:23:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T09:23:28+00:00</t>
+    <t>2026-04-27T15:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T15:12:13+00:00</t>
+    <t>2026-05-12T11:56:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:56:23+00:00</t>
+    <t>2026-05-12T13:38:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T13:38:44+00:00</t>
+    <t>2026-05-12T15:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T15:57:24+00:00</t>
+    <t>2026-05-12T16:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T16:58:28+00:00</t>
+    <t>2026-05-12T20:14:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T20:14:18+00:00</t>
+    <t>2026-05-13T09:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T09:41:30+00:00</t>
+    <t>2026-05-13T10:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T10:55:41+00:00</t>
+    <t>2026-05-18T13:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T13:45:33+00:00</t>
+    <t>2026-06-18T15:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T15:03:25+00:00</t>
+    <t>2026-06-21T11:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T11:24:04+00:00</t>
+    <t>2026-06-21T12:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T12:13:53+00:00</t>
+    <t>2026-06-21T13:26:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T13:26:08+00:00</t>
+    <t>2026-06-21T14:37:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T14:37:12+00:00</t>
+    <t>2026-06-21T15:36:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T15:36:29+00:00</t>
+    <t>2026-06-21T17:31:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T17:31:55+00:00</t>
+    <t>2026-06-21T18:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T18:39:37+00:00</t>
+    <t>2026-06-21T21:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T21:38:11+00:00</t>
+    <t>2026-06-22T02:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T02:12:35+00:00</t>
+    <t>2026-06-22T06:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T06:15:53+00:00</t>
+    <t>2026-06-22T09:45:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:45:10+00:00</t>
+    <t>2026-06-22T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:12:12+00:00</t>
+    <t>2026-06-22T20:46:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T20:46:27+00:00</t>
+    <t>2026-06-23T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T17:00:44+00:00</t>
+    <t>2026-06-24T07:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:19:56+00:00</t>
+    <t>2026-06-24T08:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:50:58+00:00</t>
+    <t>2026-06-24T10:14:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T10:14:00+00:00</t>
+    <t>2026-06-24T11:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T11:43:48+00:00</t>
+    <t>2026-06-24T13:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-atc-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:47:07+00:00</t>
+    <t>2026-06-24T15:18:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
